--- a/Schemas/ISO9001_2026.xlsx
+++ b/Schemas/ISO9001_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvih\OneDrive\Documents\LearningCodeProjects\AuditNotesWebSite\Schemas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4e7b105ed33480c9/AuditorSpace_Empty/SchemaTemplates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9698CBB0-AE6E-458B-BD5E-AE99A4B9ED41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9698CBB0-AE6E-458B-BD5E-AE99A4B9ED41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{465DAA5A-88D4-4ED5-9225-BC06D909B6DD}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,24 +269,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,20 +571,20 @@
   <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -591,7 +592,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -599,7 +600,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -607,7 +608,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -615,7 +616,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
+      <c r="A6" s="3">
         <v>4.0999999999999996</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -623,7 +624,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
+      <c r="A7" s="3">
         <v>4.2</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -631,7 +632,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
+      <c r="A8" s="3">
         <v>4.3</v>
       </c>
       <c r="B8" s="5" t="s">
@@ -639,7 +640,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
+      <c r="A9" s="3">
         <v>4.4000000000000004</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -647,7 +648,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
+      <c r="A10" s="3">
         <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -655,7 +656,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
+      <c r="A11" s="3">
         <v>5.0999999999999996</v>
       </c>
       <c r="B11" s="5" t="s">
@@ -663,7 +664,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -671,7 +672,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -679,7 +680,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
+      <c r="A14" s="3">
         <v>5.2</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -687,7 +688,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -695,7 +696,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -703,7 +704,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
+      <c r="A17" s="3">
         <v>5.3</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -711,7 +712,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
+      <c r="A18" s="3">
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -719,7 +720,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
+      <c r="A19" s="3">
         <v>6.1</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -727,7 +728,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -735,7 +736,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -743,7 +744,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -751,7 +752,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
+      <c r="A23" s="3">
         <v>6.2</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -759,7 +760,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
+      <c r="A24" s="3">
         <v>6.3</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -767,7 +768,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
+      <c r="A25" s="3">
         <v>7</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -775,7 +776,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="6">
+      <c r="A26" s="3">
         <v>7.1</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -783,7 +784,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6">
+      <c r="A27" s="3">
         <v>7.2</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -791,7 +792,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6">
+      <c r="A28" s="3">
         <v>7.3</v>
       </c>
       <c r="B28" s="5" t="s">
@@ -799,7 +800,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6">
+      <c r="A29" s="3">
         <v>7.4</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -807,7 +808,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6">
+      <c r="A30" s="3">
         <v>7.5</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -815,7 +816,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="6">
+      <c r="A31" s="3">
         <v>8</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -823,7 +824,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="6">
+      <c r="A32" s="3">
         <v>8.1</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -831,7 +832,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="6">
+      <c r="A33" s="3">
         <v>8.1999999999999993</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -839,7 +840,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="6">
+      <c r="A34" s="3">
         <v>8.3000000000000007</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -847,7 +848,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6">
+      <c r="A35" s="3">
         <v>8.4</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -855,7 +856,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="6">
+      <c r="A36" s="3">
         <v>8.5</v>
       </c>
       <c r="B36" s="5" t="s">
@@ -863,7 +864,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6">
+      <c r="A37" s="3">
         <v>8.6</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -871,7 +872,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="6">
+      <c r="A38" s="3">
         <v>8.6999999999999993</v>
       </c>
       <c r="B38" s="5" t="s">
@@ -879,7 +880,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="6">
+      <c r="A39" s="3">
         <v>9</v>
       </c>
       <c r="B39" s="5" t="s">
@@ -887,7 +888,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="6">
+      <c r="A40" s="3">
         <v>9.1</v>
       </c>
       <c r="B40" s="5" t="s">
@@ -895,7 +896,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="6">
+      <c r="A41" s="3">
         <v>9.1999999999999993</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -903,7 +904,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="6">
+      <c r="A42" s="3">
         <v>9.3000000000000007</v>
       </c>
       <c r="B42" s="5" t="s">
@@ -911,7 +912,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="6">
+      <c r="A43" s="3">
         <v>10</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -919,7 +920,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="6">
+      <c r="A44" s="3">
         <v>10.1</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -927,7 +928,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="6">
+      <c r="A45" s="3">
         <v>10.199999999999999</v>
       </c>
       <c r="B45" s="5" t="s">
